--- a/Sindhi Muslim/3rd Quarter Required Data/QPR/Hassan Panwar Goth/H. Staff Attendance/Staff Attendance.xlsx
+++ b/Sindhi Muslim/3rd Quarter Required Data/QPR/Hassan Panwar Goth/H. Staff Attendance/Staff Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\3rd Quarter Required Data\QPR\Hassan Panwar Goth\H. Staff Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF76C61-E87D-4C1A-96AA-F4243F7C22E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C29C1A1-D112-4090-B7F0-EA28642525D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="48">
   <si>
     <t>Employee Attendance Sheet</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>PST</t>
-  </si>
-  <si>
-    <t>HM</t>
   </si>
   <si>
     <t>Saleem Ahmed</t>
@@ -586,35 +583,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -626,9 +596,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -646,16 +613,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -664,7 +628,37 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -673,20 +667,23 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="15">
     <dxf>
       <font>
         <color theme="0"/>
@@ -694,6 +691,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -814,56 +831,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1157,92 +1124,92 @@
   <sheetData>
     <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:21" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="21"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="29"/>
     </row>
     <row r="3" spans="1:21" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="18" t="str">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="12" t="str">
         <f t="shared" ref="E3:P3" si="0">TEXT(E4,"ddd")</f>
         <v>Mon</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="P3" s="28" t="str">
+      <c r="P3" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="15"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="35"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1254,7 +1221,7 @@
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="7">
@@ -1290,10 +1257,10 @@
       <c r="O4" s="7">
         <v>45715</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="19">
         <v>45716</v>
       </c>
-      <c r="Q4" s="33" t="s">
+      <c r="Q4" s="22" t="s">
         <v>6</v>
       </c>
       <c r="R4" s="8" t="s">
@@ -1320,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>8</v>
@@ -1328,8 +1295,8 @@
       <c r="F5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>39</v>
+      <c r="G5" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>8</v>
@@ -1340,7 +1307,7 @@
       <c r="J5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -1355,19 +1322,19 @@
       <c r="O5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="30" t="s">
+      <c r="P5" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q5" s="3">
-        <f>COUNTIF(E5:P5,"P")</f>
+        <f t="shared" ref="Q5:Q16" si="1">COUNTIF(E5:P5,"P")</f>
         <v>5</v>
       </c>
       <c r="R5" s="4">
-        <f>COUNTIF(E5:P5,"A")</f>
+        <f t="shared" ref="R5:R16" si="2">COUNTIF(E5:P5,"A")</f>
         <v>0</v>
       </c>
       <c r="S5" s="4">
-        <f>COUNTIF(E5:P5,"L")</f>
+        <f t="shared" ref="S5:S16" si="3">COUNTIF(E5:P5,"L")</f>
         <v>5</v>
       </c>
       <c r="T5" s="4">
@@ -1397,7 +1364,7 @@
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="36"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1407,7 +1374,7 @@
       <c r="J6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="16"/>
+      <c r="K6" s="23"/>
       <c r="L6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1420,26 +1387,26 @@
       <c r="O6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="30" t="s">
+      <c r="P6" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q6" s="3">
-        <f>COUNTIF(E6:P6,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R6" s="4">
-        <f>COUNTIF(E6:P6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S6" s="4">
-        <f>COUNTIF(E6:P6,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T6" s="4">
         <v>1</v>
       </c>
       <c r="U6" s="10">
-        <f t="shared" ref="U6:U15" si="1">Q6+S6+T6</f>
+        <f t="shared" ref="U6:U15" si="4">Q6+S6+T6</f>
         <v>11</v>
       </c>
     </row>
@@ -1462,7 +1429,7 @@
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1472,7 +1439,7 @@
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="23"/>
       <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
@@ -1485,26 +1452,26 @@
       <c r="O7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P7" s="30" t="s">
+      <c r="P7" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q7" s="3">
-        <f>COUNTIF(E7:P7,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R7" s="4">
-        <f>COUNTIF(E7:P7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S7" s="4">
-        <f>COUNTIF(E7:P7,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T7" s="4">
         <v>1</v>
       </c>
       <c r="U7" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
@@ -1513,10 +1480,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>27</v>
@@ -1527,7 +1494,7 @@
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="36"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1537,7 +1504,7 @@
       <c r="J8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="16"/>
+      <c r="K8" s="23"/>
       <c r="L8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1550,26 +1517,26 @@
       <c r="O8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P8" s="30" t="s">
+      <c r="P8" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q8" s="3">
-        <f>COUNTIF(E8:P8,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="R8" s="4">
-        <f>COUNTIF(E8:P8,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S8" s="4">
-        <f>COUNTIF(E8:P8,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T8" s="4">
         <v>1</v>
       </c>
       <c r="U8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
@@ -1592,7 +1559,7 @@
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="36"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1602,7 +1569,7 @@
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K9" s="16"/>
+      <c r="K9" s="23"/>
       <c r="L9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1615,26 +1582,26 @@
       <c r="O9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="P9" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q9" s="3">
-        <f>COUNTIF(E9:P9,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="R9" s="4">
-        <f>COUNTIF(E9:P9,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S9" s="4">
-        <f>COUNTIF(E9:P9,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T9" s="4">
         <v>1</v>
       </c>
       <c r="U9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
@@ -1646,7 +1613,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>27</v>
@@ -1657,7 +1624,7 @@
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="36"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="4" t="s">
         <v>6</v>
       </c>
@@ -1667,7 +1634,7 @@
       <c r="J10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="16"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="4" t="s">
         <v>6</v>
       </c>
@@ -1680,26 +1647,26 @@
       <c r="O10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="30" t="s">
+      <c r="P10" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q10" s="3">
-        <f>COUNTIF(E10:P10,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R10" s="4">
-        <f>COUNTIF(E10:P10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S10" s="4">
-        <f>COUNTIF(E10:P10,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T10" s="4">
         <v>1</v>
       </c>
       <c r="U10" s="10">
-        <f t="shared" ref="U10:U11" si="2">Q10+S10+T10</f>
+        <f t="shared" ref="U10:U11" si="5">Q10+S10+T10</f>
         <v>11</v>
       </c>
     </row>
@@ -1708,10 +1675,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>27</v>
@@ -1722,7 +1689,7 @@
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="36"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="4" t="s">
         <v>6</v>
       </c>
@@ -1732,7 +1699,7 @@
       <c r="J11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="16"/>
+      <c r="K11" s="23"/>
       <c r="L11" s="4" t="s">
         <v>6</v>
       </c>
@@ -1745,26 +1712,26 @@
       <c r="O11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P11" s="30" t="s">
+      <c r="P11" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q11" s="3">
-        <f>COUNTIF(E11:P11,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R11" s="4">
-        <f>COUNTIF(E11:P11,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S11" s="4">
-        <f>COUNTIF(E11:P11,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T11" s="4">
         <v>1</v>
       </c>
       <c r="U11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
@@ -1787,7 +1754,7 @@
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="36"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="4" t="s">
         <v>6</v>
       </c>
@@ -1797,7 +1764,7 @@
       <c r="J12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="16"/>
+      <c r="K12" s="23"/>
       <c r="L12" s="4" t="s">
         <v>8</v>
       </c>
@@ -1810,26 +1777,26 @@
       <c r="O12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P12" s="30" t="s">
+      <c r="P12" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q12" s="3">
-        <f>COUNTIF(E12:P12,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="R12" s="4">
-        <f>COUNTIF(E12:P12,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S12" s="4">
-        <f>COUNTIF(E12:P12,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T12" s="4">
         <v>1</v>
       </c>
       <c r="U12" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
@@ -1852,7 +1819,7 @@
       <c r="F13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="36"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="4" t="s">
         <v>6</v>
       </c>
@@ -1862,7 +1829,7 @@
       <c r="J13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="16"/>
+      <c r="K13" s="23"/>
       <c r="L13" s="4" t="s">
         <v>6</v>
       </c>
@@ -1875,26 +1842,26 @@
       <c r="O13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P13" s="30" t="s">
+      <c r="P13" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q13" s="3">
-        <f>COUNTIF(E13:P13,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R13" s="4">
-        <f>COUNTIF(E13:P13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S13" s="4">
-        <f>COUNTIF(E13:P13,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T13" s="4">
         <v>1</v>
       </c>
       <c r="U13" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
@@ -1917,7 +1884,7 @@
       <c r="F14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="4" t="s">
         <v>6</v>
       </c>
@@ -1927,7 +1894,7 @@
       <c r="J14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="23"/>
       <c r="L14" s="4" t="s">
         <v>8</v>
       </c>
@@ -1940,26 +1907,26 @@
       <c r="O14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P14" s="30" t="s">
+      <c r="P14" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q14" s="3">
-        <f>COUNTIF(E14:P14,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="R14" s="4">
-        <f>COUNTIF(E14:P14,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="4">
-        <f>COUNTIF(E14:P14,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T14" s="4">
         <v>1</v>
       </c>
       <c r="U14" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
@@ -1968,13 +1935,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="D15" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>6</v>
@@ -1982,7 +1949,7 @@
       <c r="F15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="36"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="4" t="s">
         <v>8</v>
       </c>
@@ -1992,7 +1959,7 @@
       <c r="J15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="16"/>
+      <c r="K15" s="23"/>
       <c r="L15" s="4" t="s">
         <v>6</v>
       </c>
@@ -2005,26 +1972,26 @@
       <c r="O15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P15" s="30" t="s">
+      <c r="P15" s="20" t="s">
         <v>6</v>
       </c>
       <c r="Q15" s="3">
-        <f>COUNTIF(E15:P15,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="R15" s="4">
-        <f>COUNTIF(E15:P15,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S15" s="4">
-        <f>COUNTIF(E15:P15,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="T15" s="4">
         <v>1</v>
       </c>
       <c r="U15" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
     </row>
@@ -2033,21 +2000,21 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="37"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="6" t="s">
         <v>6</v>
       </c>
@@ -2057,7 +2024,7 @@
       <c r="J16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="17"/>
+      <c r="K16" s="24"/>
       <c r="L16" s="6" t="s">
         <v>6</v>
       </c>
@@ -2070,26 +2037,26 @@
       <c r="O16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P16" s="31" t="s">
+      <c r="P16" s="21" t="s">
         <v>6</v>
       </c>
       <c r="Q16" s="5">
-        <f>COUNTIF(E16:P16,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="R16" s="6">
-        <f>COUNTIF(E16:P16,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <f>COUNTIF(E16:P16,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
       <c r="U16" s="11">
-        <f t="shared" ref="U16" si="3">Q16+S16+T16</f>
+        <f t="shared" ref="U16" si="6">Q16+S16+T16</f>
         <v>10</v>
       </c>
     </row>
@@ -2101,17 +2068,17 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="Q3:U3"/>
   </mergeCells>
-  <conditionalFormatting sqref="K5 E5:F16 L5:P16 H5:J16 G5">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+  <conditionalFormatting sqref="E3:P4 G5 K5 E5:F16 H5:J16 L5:P16">
+    <cfRule type="expression" dxfId="14" priority="1">
+      <formula>E$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5 K5 E5:F16 H5:J16 L5:P16">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K5 E5:F16 L5:P16 E3:P4 H5:J16 G5">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>E$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2138,187 +2105,187 @@
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:40" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
-      <c r="AM2" s="20"/>
-      <c r="AN2" s="21"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="29"/>
     </row>
     <row r="3" spans="1:40" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="22" t="str">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="13" t="str">
         <f>TEXT(E4,"ddd")</f>
         <v>Sat</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="12" t="str">
         <f t="shared" ref="F3:AI3" si="0">TEXT(F4,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="P3" s="18" t="str">
+      <c r="P3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="Q3" s="18" t="str">
+      <c r="Q3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="R3" s="18" t="str">
+      <c r="R3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="S3" s="18" t="str">
+      <c r="S3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="T3" s="18" t="str">
+      <c r="T3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="U3" s="18" t="str">
+      <c r="U3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="V3" s="18" t="str">
+      <c r="V3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="W3" s="18" t="str">
+      <c r="W3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="X3" s="18" t="str">
+      <c r="X3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="Y3" s="18" t="str">
+      <c r="Y3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="Z3" s="18" t="str">
+      <c r="Z3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AA3" s="18" t="str">
+      <c r="AA3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AB3" s="18" t="str">
+      <c r="AB3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AC3" s="18" t="str">
+      <c r="AC3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AD3" s="18" t="str">
+      <c r="AD3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AE3" s="18" t="str">
+      <c r="AE3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AF3" s="18" t="str">
+      <c r="AF3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AG3" s="18" t="str">
+      <c r="AG3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AH3" s="18" t="str">
+      <c r="AH3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AI3" s="28" t="str">
+      <c r="AI3" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AJ3" s="32" t="s">
+      <c r="AJ3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="15"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="34"/>
+      <c r="AN3" s="35"/>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2330,10 +2297,10 @@
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="14">
         <v>45717</v>
       </c>
       <c r="F4" s="7">
@@ -2423,10 +2390,10 @@
       <c r="AH4" s="7">
         <v>45746</v>
       </c>
-      <c r="AI4" s="29">
+      <c r="AI4" s="19">
         <v>45747</v>
       </c>
-      <c r="AJ4" s="33" t="s">
+      <c r="AJ4" s="22" t="s">
         <v>6</v>
       </c>
       <c r="AK4" s="8" t="s">
@@ -2453,12 +2420,12 @@
         <v>14</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -2479,7 +2446,7 @@
       <c r="L5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="4" t="s">
@@ -2500,7 +2467,7 @@
       <c r="S5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T5" s="16" t="s">
+      <c r="T5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="U5" s="4" t="s">
@@ -2518,35 +2485,35 @@
       <c r="Y5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="38" t="s">
+      <c r="Z5" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="AA5" s="16" t="s">
+      <c r="AH5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AB5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG5" s="39" t="s">
+      <c r="AI5" s="40" t="s">
         <v>42</v>
-      </c>
-      <c r="AH5" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI5" s="42" t="s">
-        <v>43</v>
       </c>
       <c r="AJ5" s="3">
         <f>COUNTIF(E5:AI5,"P")</f>
@@ -2581,10 +2548,10 @@
       <c r="D6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="16"/>
+      <c r="E6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="23"/>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2603,7 +2570,7 @@
       <c r="L6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="16"/>
+      <c r="M6" s="23"/>
       <c r="N6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2622,7 +2589,7 @@
       <c r="S6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T6" s="16"/>
+      <c r="T6" s="23"/>
       <c r="U6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2638,8 +2605,8 @@
       <c r="Y6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="16"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="23"/>
       <c r="AB6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2655,9 +2622,9 @@
       <c r="AF6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="16"/>
-      <c r="AI6" s="42"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="40"/>
       <c r="AJ6" s="3">
         <f>COUNTIF(E6:AI6,"P")</f>
         <v>22</v>
@@ -2692,10 +2659,10 @@
       <c r="D7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="16"/>
+      <c r="E7" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="23"/>
       <c r="G7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2714,7 +2681,7 @@
       <c r="L7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="16"/>
+      <c r="M7" s="23"/>
       <c r="N7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2733,7 +2700,7 @@
       <c r="S7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="16"/>
+      <c r="T7" s="23"/>
       <c r="U7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2749,8 +2716,8 @@
       <c r="Y7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="16"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="23"/>
       <c r="AB7" s="4" t="s">
         <v>8</v>
       </c>
@@ -2766,9 +2733,9 @@
       <c r="AF7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="16"/>
-      <c r="AI7" s="42"/>
+      <c r="AG7" s="38"/>
+      <c r="AH7" s="23"/>
+      <c r="AI7" s="40"/>
       <c r="AJ7" s="3">
         <f>COUNTIF(E7:AI7,"P")</f>
         <v>22</v>
@@ -2795,18 +2762,18 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="16"/>
+      <c r="E8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="23"/>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2825,7 +2792,7 @@
       <c r="L8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M8" s="16"/>
+      <c r="M8" s="23"/>
       <c r="N8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2844,7 +2811,7 @@
       <c r="S8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T8" s="16"/>
+      <c r="T8" s="23"/>
       <c r="U8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2860,8 +2827,8 @@
       <c r="Y8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="16"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="23"/>
       <c r="AB8" s="4" t="s">
         <v>6</v>
       </c>
@@ -2877,9 +2844,9 @@
       <c r="AF8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG8" s="39"/>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="42"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="40"/>
       <c r="AJ8" s="3">
         <f>COUNTIF(E8:AI8,"P")</f>
         <v>22</v>
@@ -2914,10 +2881,10 @@
       <c r="D9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="16"/>
+      <c r="E9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="23"/>
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2936,7 +2903,7 @@
       <c r="L9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="16"/>
+      <c r="M9" s="23"/>
       <c r="N9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2955,7 +2922,7 @@
       <c r="S9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="16"/>
+      <c r="T9" s="23"/>
       <c r="U9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2971,8 +2938,8 @@
       <c r="Y9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="16"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="23"/>
       <c r="AB9" s="4" t="s">
         <v>6</v>
       </c>
@@ -2988,9 +2955,9 @@
       <c r="AF9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG9" s="39"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="42"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="23"/>
+      <c r="AI9" s="40"/>
       <c r="AJ9" s="3">
         <f>COUNTIF(E9:AI9,"P")</f>
         <v>21</v>
@@ -3020,15 +2987,15 @@
         <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="16"/>
+      <c r="E10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="23"/>
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3047,7 +3014,7 @@
       <c r="L10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="16"/>
+      <c r="M10" s="23"/>
       <c r="N10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3066,7 +3033,7 @@
       <c r="S10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T10" s="16"/>
+      <c r="T10" s="23"/>
       <c r="U10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3082,8 +3049,8 @@
       <c r="Y10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="16"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="23"/>
       <c r="AB10" s="4" t="s">
         <v>6</v>
       </c>
@@ -3099,9 +3066,9 @@
       <c r="AF10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="16"/>
-      <c r="AI10" s="42"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="23"/>
+      <c r="AI10" s="40"/>
       <c r="AJ10" s="3">
         <f t="shared" ref="AJ10:AJ11" si="2">COUNTIF(E10:AI10,"P")</f>
         <v>23</v>
@@ -3128,18 +3095,18 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="16"/>
+      <c r="E11" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="23"/>
       <c r="G11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3158,7 +3125,7 @@
       <c r="L11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M11" s="16"/>
+      <c r="M11" s="23"/>
       <c r="N11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3177,7 +3144,7 @@
       <c r="S11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T11" s="16"/>
+      <c r="T11" s="23"/>
       <c r="U11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3193,8 +3160,8 @@
       <c r="Y11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="16"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="23"/>
       <c r="AB11" s="4" t="s">
         <v>6</v>
       </c>
@@ -3210,9 +3177,9 @@
       <c r="AF11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="42"/>
+      <c r="AG11" s="38"/>
+      <c r="AH11" s="23"/>
+      <c r="AI11" s="40"/>
       <c r="AJ11" s="3">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -3247,10 +3214,10 @@
       <c r="D12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="16"/>
+      <c r="E12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="23"/>
       <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
@@ -3269,7 +3236,7 @@
       <c r="L12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M12" s="16"/>
+      <c r="M12" s="23"/>
       <c r="N12" s="4" t="s">
         <v>6</v>
       </c>
@@ -3288,7 +3255,7 @@
       <c r="S12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T12" s="16"/>
+      <c r="T12" s="23"/>
       <c r="U12" s="4" t="s">
         <v>6</v>
       </c>
@@ -3304,8 +3271,8 @@
       <c r="Y12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="16"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="23"/>
       <c r="AB12" s="4" t="s">
         <v>6</v>
       </c>
@@ -3321,9 +3288,9 @@
       <c r="AF12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="16"/>
-      <c r="AI12" s="42"/>
+      <c r="AG12" s="38"/>
+      <c r="AH12" s="23"/>
+      <c r="AI12" s="40"/>
       <c r="AJ12" s="3">
         <f>COUNTIF(E12:AI12,"P")</f>
         <v>22</v>
@@ -3358,10 +3325,10 @@
       <c r="D13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="16"/>
+      <c r="E13" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="23"/>
       <c r="G13" s="4" t="s">
         <v>6</v>
       </c>
@@ -3380,7 +3347,7 @@
       <c r="L13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M13" s="16"/>
+      <c r="M13" s="23"/>
       <c r="N13" s="4" t="s">
         <v>6</v>
       </c>
@@ -3399,7 +3366,7 @@
       <c r="S13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T13" s="16"/>
+      <c r="T13" s="23"/>
       <c r="U13" s="4" t="s">
         <v>6</v>
       </c>
@@ -3415,8 +3382,8 @@
       <c r="Y13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="16"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="23"/>
       <c r="AB13" s="4" t="s">
         <v>6</v>
       </c>
@@ -3432,9 +3399,9 @@
       <c r="AF13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG13" s="39"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="42"/>
+      <c r="AG13" s="38"/>
+      <c r="AH13" s="23"/>
+      <c r="AI13" s="40"/>
       <c r="AJ13" s="3">
         <f>COUNTIF(E13:AI13,"P")</f>
         <v>21</v>
@@ -3469,10 +3436,10 @@
       <c r="D14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="16"/>
+      <c r="E14" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="23"/>
       <c r="G14" s="4" t="s">
         <v>6</v>
       </c>
@@ -3491,7 +3458,7 @@
       <c r="L14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M14" s="16"/>
+      <c r="M14" s="23"/>
       <c r="N14" s="4" t="s">
         <v>6</v>
       </c>
@@ -3510,7 +3477,7 @@
       <c r="S14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="16"/>
+      <c r="T14" s="23"/>
       <c r="U14" s="4" t="s">
         <v>6</v>
       </c>
@@ -3526,8 +3493,8 @@
       <c r="Y14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z14" s="38"/>
-      <c r="AA14" s="16"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="23"/>
       <c r="AB14" s="4" t="s">
         <v>6</v>
       </c>
@@ -3543,9 +3510,9 @@
       <c r="AF14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="16"/>
-      <c r="AI14" s="42"/>
+      <c r="AG14" s="38"/>
+      <c r="AH14" s="23"/>
+      <c r="AI14" s="40"/>
       <c r="AJ14" s="3">
         <f>COUNTIF(E14:AI14,"P")</f>
         <v>21</v>
@@ -3572,18 +3539,18 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="16"/>
+      <c r="E15" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="23"/>
       <c r="G15" s="4" t="s">
         <v>6</v>
       </c>
@@ -3602,7 +3569,7 @@
       <c r="L15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="16"/>
+      <c r="M15" s="23"/>
       <c r="N15" s="4" t="s">
         <v>6</v>
       </c>
@@ -3621,7 +3588,7 @@
       <c r="S15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T15" s="16"/>
+      <c r="T15" s="23"/>
       <c r="U15" s="4" t="s">
         <v>6</v>
       </c>
@@ -3637,8 +3604,8 @@
       <c r="Y15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z15" s="38"/>
-      <c r="AA15" s="16"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="23"/>
       <c r="AB15" s="4" t="s">
         <v>6</v>
       </c>
@@ -3654,9 +3621,9 @@
       <c r="AF15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="16"/>
-      <c r="AI15" s="42"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="23"/>
+      <c r="AI15" s="40"/>
       <c r="AJ15" s="3">
         <f>COUNTIF(E15:AI15,"P")</f>
         <v>23</v>
@@ -3683,18 +3650,18 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="D16" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="16"/>
+        <v>32</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="23"/>
       <c r="G16" s="4" t="s">
         <v>6</v>
       </c>
@@ -3713,7 +3680,7 @@
       <c r="L16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M16" s="16"/>
+      <c r="M16" s="23"/>
       <c r="N16" s="4" t="s">
         <v>6</v>
       </c>
@@ -3732,7 +3699,7 @@
       <c r="S16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T16" s="16"/>
+      <c r="T16" s="23"/>
       <c r="U16" s="4" t="s">
         <v>6</v>
       </c>
@@ -3748,8 +3715,8 @@
       <c r="Y16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z16" s="38"/>
-      <c r="AA16" s="16"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="23"/>
       <c r="AB16" s="4" t="s">
         <v>6</v>
       </c>
@@ -3765,9 +3732,9 @@
       <c r="AF16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG16" s="39"/>
-      <c r="AH16" s="16"/>
-      <c r="AI16" s="42"/>
+      <c r="AG16" s="38"/>
+      <c r="AH16" s="23"/>
+      <c r="AI16" s="40"/>
       <c r="AJ16" s="3">
         <f>COUNTIF(E16:AI16,"P")</f>
         <v>21</v>
@@ -3794,18 +3761,18 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="16"/>
+      <c r="E17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="23"/>
       <c r="G17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3824,7 +3791,7 @@
       <c r="L17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="23"/>
       <c r="N17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3843,7 +3810,7 @@
       <c r="S17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="T17" s="16"/>
+      <c r="T17" s="23"/>
       <c r="U17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3859,8 +3826,8 @@
       <c r="Y17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="16"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="23"/>
       <c r="AB17" s="4" t="s">
         <v>6</v>
       </c>
@@ -3876,9 +3843,9 @@
       <c r="AF17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AG17" s="39"/>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="42"/>
+      <c r="AG17" s="38"/>
+      <c r="AH17" s="23"/>
+      <c r="AI17" s="40"/>
       <c r="AJ17" s="3">
         <f t="shared" ref="AJ17:AJ18" si="6">COUNTIF(E17:AI17,"P")</f>
         <v>23</v>
@@ -3905,26 +3872,26 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="17"/>
+      <c r="E18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="24"/>
       <c r="G18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>6</v>
@@ -3935,7 +3902,7 @@
       <c r="L18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="17"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="6" t="s">
         <v>6</v>
       </c>
@@ -3954,7 +3921,7 @@
       <c r="S18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T18" s="17"/>
+      <c r="T18" s="24"/>
       <c r="U18" s="6" t="s">
         <v>6</v>
       </c>
@@ -3970,8 +3937,8 @@
       <c r="Y18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z18" s="41"/>
-      <c r="AA18" s="17"/>
+      <c r="Z18" s="37"/>
+      <c r="AA18" s="24"/>
       <c r="AB18" s="6" t="s">
         <v>6</v>
       </c>
@@ -3987,9 +3954,9 @@
       <c r="AF18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AG18" s="40"/>
-      <c r="AH18" s="17"/>
-      <c r="AI18" s="43"/>
+      <c r="AG18" s="39"/>
+      <c r="AH18" s="24"/>
+      <c r="AI18" s="41"/>
       <c r="AJ18" s="5">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -4013,29 +3980,29 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F5:F18"/>
-    <mergeCell ref="M5:M18"/>
-    <mergeCell ref="T5:T18"/>
-    <mergeCell ref="Z5:Z18"/>
-    <mergeCell ref="AA5:AA18"/>
     <mergeCell ref="AG5:AG18"/>
     <mergeCell ref="AH5:AH18"/>
     <mergeCell ref="AI5:AI18"/>
     <mergeCell ref="A2:AN2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="F5:F18"/>
+    <mergeCell ref="M5:M18"/>
+    <mergeCell ref="T5:T18"/>
+    <mergeCell ref="Z5:Z18"/>
+    <mergeCell ref="AA5:AA18"/>
   </mergeCells>
+  <conditionalFormatting sqref="E3:AI4 F5 M5 T5 Z5:AA5 AG5:AI5 E5:E18 G5:L18 N5:S18 U5:Y18 AB5:AF18">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>E$3="SUN"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F5 M5 T5 Z5:AA5 AG5:AI5 E5:E18 G5:L18 N5:S18 U5:Y18 AB5:AF18">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5 M5 T5 E3:AI4 Z5:AA5 AG5:AI5 E5:E18 G5:L18 N5:S18 U5:Y18 AB5:AF18">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>E$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4062,182 +4029,182 @@
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:39" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
-      <c r="AM2" s="21"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="29"/>
     </row>
     <row r="3" spans="1:39" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="22" t="str">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="13" t="str">
         <f>TEXT(E4,"ddd")</f>
         <v>Tue</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="12" t="str">
         <f t="shared" ref="F3:AH3" si="0">TEXT(F4,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="P3" s="18" t="str">
+      <c r="P3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="Q3" s="18" t="str">
+      <c r="Q3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="R3" s="18" t="str">
+      <c r="R3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="S3" s="18" t="str">
+      <c r="S3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="T3" s="18" t="str">
+      <c r="T3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="U3" s="18" t="str">
+      <c r="U3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="V3" s="18" t="str">
+      <c r="V3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="W3" s="18" t="str">
+      <c r="W3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="X3" s="18" t="str">
+      <c r="X3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="Y3" s="18" t="str">
+      <c r="Y3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="Z3" s="18" t="str">
+      <c r="Z3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AA3" s="18" t="str">
+      <c r="AA3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AB3" s="18" t="str">
+      <c r="AB3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AC3" s="18" t="str">
+      <c r="AC3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AD3" s="18" t="str">
+      <c r="AD3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AE3" s="18" t="str">
+      <c r="AE3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AF3" s="18" t="str">
+      <c r="AF3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AG3" s="18" t="str">
+      <c r="AG3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AH3" s="28" t="str">
+      <c r="AH3" s="18" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AI3" s="32" t="s">
+      <c r="AI3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="15"/>
+      <c r="AJ3" s="34"/>
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="35"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -4249,10 +4216,10 @@
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="14">
         <v>45748</v>
       </c>
       <c r="F4" s="7">
@@ -4339,10 +4306,10 @@
       <c r="AG4" s="7">
         <v>45776</v>
       </c>
-      <c r="AH4" s="29">
+      <c r="AH4" s="19">
         <v>45777</v>
       </c>
-      <c r="AI4" s="33" t="s">
+      <c r="AI4" s="22" t="s">
         <v>6</v>
       </c>
       <c r="AJ4" s="8" t="s">
@@ -4369,13 +4336,13 @@
         <v>14</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>43</v>
+        <v>27</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>42</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>6</v>
@@ -4386,7 +4353,7 @@
       <c r="I5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -4407,7 +4374,7 @@
       <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="Q5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="R5" s="4" t="s">
@@ -4428,7 +4395,7 @@
       <c r="W5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X5" s="16" t="s">
+      <c r="X5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="Y5" s="4" t="s">
@@ -4449,7 +4416,7 @@
       <c r="AD5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE5" s="16" t="s">
+      <c r="AE5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="AF5" s="4" t="s">
@@ -4458,19 +4425,19 @@
       <c r="AG5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH5" s="30" t="s">
+      <c r="AH5" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI5" s="3">
-        <f>COUNTIF(E5:AH5,"P")</f>
+        <f t="shared" ref="AI5:AI18" si="1">COUNTIF(E5:AH5,"P")</f>
         <v>22</v>
       </c>
       <c r="AJ5" s="4">
-        <f>COUNTIF(E5:AH5,"A")</f>
+        <f t="shared" ref="AJ5:AJ18" si="2">COUNTIF(E5:AH5,"A")</f>
         <v>0</v>
       </c>
       <c r="AK5" s="4">
-        <f>COUNTIF(E5:AH5,"L")</f>
+        <f t="shared" ref="AK5:AK18" si="3">COUNTIF(E5:AH5,"L")</f>
         <v>2</v>
       </c>
       <c r="AL5" s="4">
@@ -4494,8 +4461,8 @@
       <c r="D6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4505,7 +4472,7 @@
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="16"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4524,7 +4491,7 @@
       <c r="P6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="16"/>
+      <c r="Q6" s="23"/>
       <c r="R6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4543,7 +4510,7 @@
       <c r="W6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X6" s="16"/>
+      <c r="X6" s="23"/>
       <c r="Y6" s="4" t="s">
         <v>8</v>
       </c>
@@ -4562,34 +4529,34 @@
       <c r="AD6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE6" s="16"/>
+      <c r="AE6" s="23"/>
       <c r="AF6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="AG6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH6" s="30" t="s">
+      <c r="AH6" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI6" s="3">
-        <f>COUNTIF(E6:AH6,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ6" s="4">
-        <f>COUNTIF(E6:AH6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK6" s="4">
-        <f>COUNTIF(E6:AH6,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL6" s="4">
-        <f>COUNTBLANK(E6:AH6)</f>
+        <f t="shared" ref="AL6:AL18" si="4">COUNTBLANK(E6:AH6)</f>
         <v>6</v>
       </c>
       <c r="AM6" s="10">
-        <f t="shared" ref="AM6:AM17" si="1">AI6+AK6+AL6</f>
+        <f t="shared" ref="AM6:AM17" si="5">AI6+AK6+AL6</f>
         <v>30</v>
       </c>
     </row>
@@ -4598,16 +4565,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
       <c r="G7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4617,7 +4584,7 @@
       <c r="I7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="16"/>
+      <c r="J7" s="23"/>
       <c r="K7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4636,7 +4603,7 @@
       <c r="P7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q7" s="16"/>
+      <c r="Q7" s="23"/>
       <c r="R7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4655,7 +4622,7 @@
       <c r="W7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X7" s="16"/>
+      <c r="X7" s="23"/>
       <c r="Y7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4674,34 +4641,34 @@
       <c r="AD7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="AE7" s="16"/>
+      <c r="AE7" s="23"/>
       <c r="AF7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH7" s="30" t="s">
+      <c r="AH7" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI7" s="3">
-        <f>COUNTIF(E7:AH7,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ7" s="4">
-        <f>COUNTIF(E7:AH7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK7" s="4">
-        <f>COUNTIF(E7:AH7,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL7" s="4">
-        <f>COUNTBLANK(E7:AH7)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM7" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -4718,8 +4685,8 @@
       <c r="D8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4729,7 +4696,7 @@
       <c r="I8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="16"/>
+      <c r="J8" s="23"/>
       <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4748,7 +4715,7 @@
       <c r="P8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q8" s="16"/>
+      <c r="Q8" s="23"/>
       <c r="R8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4767,7 +4734,7 @@
       <c r="W8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X8" s="16"/>
+      <c r="X8" s="23"/>
       <c r="Y8" s="4" t="s">
         <v>8</v>
       </c>
@@ -4786,34 +4753,34 @@
       <c r="AD8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE8" s="16"/>
+      <c r="AE8" s="23"/>
       <c r="AF8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH8" s="30" t="s">
+      <c r="AH8" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI8" s="3">
-        <f>COUNTIF(E8:AH8,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ8" s="4">
-        <f>COUNTIF(E8:AH8,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK8" s="4">
-        <f>COUNTIF(E8:AH8,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL8" s="4">
-        <f>COUNTBLANK(E8:AH8)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -4825,13 +4792,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
       <c r="G9" s="4" t="s">
         <v>8</v>
       </c>
@@ -4841,7 +4808,7 @@
       <c r="I9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="16"/>
+      <c r="J9" s="23"/>
       <c r="K9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4860,7 +4827,7 @@
       <c r="P9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q9" s="16"/>
+      <c r="Q9" s="23"/>
       <c r="R9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4879,7 +4846,7 @@
       <c r="W9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X9" s="16"/>
+      <c r="X9" s="23"/>
       <c r="Y9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4898,34 +4865,34 @@
       <c r="AD9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE9" s="16"/>
+      <c r="AE9" s="23"/>
       <c r="AF9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH9" s="30" t="s">
+      <c r="AH9" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI9" s="3">
-        <f>COUNTIF(E9:AH9,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ9" s="4">
-        <f>COUNTIF(E9:AH9,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK9" s="4">
-        <f>COUNTIF(E9:AH9,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL9" s="4">
-        <f>COUNTBLANK(E9:AH9)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -4934,16 +4901,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
@@ -4953,7 +4920,7 @@
       <c r="I10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="16"/>
+      <c r="J10" s="23"/>
       <c r="K10" s="4" t="s">
         <v>6</v>
       </c>
@@ -4972,7 +4939,7 @@
       <c r="P10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q10" s="16"/>
+      <c r="Q10" s="23"/>
       <c r="R10" s="4" t="s">
         <v>6</v>
       </c>
@@ -4991,7 +4958,7 @@
       <c r="W10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X10" s="16"/>
+      <c r="X10" s="23"/>
       <c r="Y10" s="4" t="s">
         <v>6</v>
       </c>
@@ -5010,34 +4977,34 @@
       <c r="AD10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE10" s="16"/>
+      <c r="AE10" s="23"/>
       <c r="AF10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH10" s="30" t="s">
+      <c r="AH10" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI10" s="3">
-        <f>COUNTIF(E10:AH10,"P")</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="AJ10" s="4">
-        <f>COUNTIF(E10:AH10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK10" s="4">
-        <f>COUNTIF(E10:AH10,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL10" s="4">
-        <f>COUNTBLANK(E10:AH10)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -5046,16 +5013,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5065,7 +5032,7 @@
       <c r="I11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="16"/>
+      <c r="J11" s="23"/>
       <c r="K11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5084,7 +5051,7 @@
       <c r="P11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q11" s="16"/>
+      <c r="Q11" s="23"/>
       <c r="R11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5103,7 +5070,7 @@
       <c r="W11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X11" s="16"/>
+      <c r="X11" s="23"/>
       <c r="Y11" s="4" t="s">
         <v>6</v>
       </c>
@@ -5122,34 +5089,34 @@
       <c r="AD11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE11" s="16"/>
+      <c r="AE11" s="23"/>
       <c r="AF11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH11" s="30" t="s">
+      <c r="AH11" s="20" t="s">
         <v>8</v>
       </c>
       <c r="AI11" s="3">
-        <f>COUNTIF(E11:AH11,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ11" s="4">
-        <f>COUNTIF(E11:AH11,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK11" s="4">
-        <f>COUNTIF(E11:AH11,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL11" s="4">
-        <f>COUNTBLANK(E11:AH11)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -5166,8 +5133,8 @@
       <c r="D12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
@@ -5177,7 +5144,7 @@
       <c r="I12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="16"/>
+      <c r="J12" s="23"/>
       <c r="K12" s="4" t="s">
         <v>6</v>
       </c>
@@ -5196,7 +5163,7 @@
       <c r="P12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q12" s="16"/>
+      <c r="Q12" s="23"/>
       <c r="R12" s="4" t="s">
         <v>6</v>
       </c>
@@ -5215,7 +5182,7 @@
       <c r="W12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X12" s="16"/>
+      <c r="X12" s="23"/>
       <c r="Y12" s="4" t="s">
         <v>6</v>
       </c>
@@ -5234,34 +5201,34 @@
       <c r="AD12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE12" s="16"/>
+      <c r="AE12" s="23"/>
       <c r="AF12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH12" s="30" t="s">
+      <c r="AH12" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI12" s="3">
-        <f>COUNTIF(E12:AH12,"P")</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="AJ12" s="4">
-        <f>COUNTIF(E12:AH12,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK12" s="4">
-        <f>COUNTIF(E12:AH12,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL12" s="4">
-        <f>COUNTBLANK(E12:AH12)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM12" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -5278,8 +5245,8 @@
       <c r="D13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="4" t="s">
         <v>6</v>
       </c>
@@ -5289,7 +5256,7 @@
       <c r="I13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="16"/>
+      <c r="J13" s="23"/>
       <c r="K13" s="4" t="s">
         <v>6</v>
       </c>
@@ -5308,7 +5275,7 @@
       <c r="P13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q13" s="16"/>
+      <c r="Q13" s="23"/>
       <c r="R13" s="4" t="s">
         <v>6</v>
       </c>
@@ -5327,7 +5294,7 @@
       <c r="W13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="X13" s="16"/>
+      <c r="X13" s="23"/>
       <c r="Y13" s="4" t="s">
         <v>6</v>
       </c>
@@ -5346,34 +5313,34 @@
       <c r="AD13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE13" s="16"/>
+      <c r="AE13" s="23"/>
       <c r="AF13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH13" s="30" t="s">
+      <c r="AH13" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI13" s="3">
-        <f>COUNTIF(E13:AH13,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ13" s="4">
-        <f>COUNTIF(E13:AH13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK13" s="4">
-        <f>COUNTIF(E13:AH13,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL13" s="4">
-        <f>COUNTBLANK(E13:AH13)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM13" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -5390,8 +5357,8 @@
       <c r="D14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="4" t="s">
         <v>8</v>
       </c>
@@ -5401,7 +5368,7 @@
       <c r="I14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="16"/>
+      <c r="J14" s="23"/>
       <c r="K14" s="4" t="s">
         <v>8</v>
       </c>
@@ -5420,7 +5387,7 @@
       <c r="P14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q14" s="16"/>
+      <c r="Q14" s="23"/>
       <c r="R14" s="4" t="s">
         <v>6</v>
       </c>
@@ -5439,7 +5406,7 @@
       <c r="W14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X14" s="16"/>
+      <c r="X14" s="23"/>
       <c r="Y14" s="4" t="s">
         <v>6</v>
       </c>
@@ -5458,34 +5425,34 @@
       <c r="AD14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE14" s="16"/>
+      <c r="AE14" s="23"/>
       <c r="AF14" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH14" s="30" t="s">
+      <c r="AH14" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI14" s="3">
-        <f>COUNTIF(E14:AH14,"P")</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AJ14" s="4">
-        <f>COUNTIF(E14:AH14,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK14" s="4">
-        <f>COUNTIF(E14:AH14,"L")</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="AL14" s="4">
-        <f>COUNTBLANK(E14:AH14)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM14" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -5494,16 +5461,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="4" t="s">
         <v>6</v>
       </c>
@@ -5513,7 +5480,7 @@
       <c r="I15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="16"/>
+      <c r="J15" s="23"/>
       <c r="K15" s="4" t="s">
         <v>6</v>
       </c>
@@ -5532,7 +5499,7 @@
       <c r="P15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q15" s="16"/>
+      <c r="Q15" s="23"/>
       <c r="R15" s="4" t="s">
         <v>6</v>
       </c>
@@ -5551,7 +5518,7 @@
       <c r="W15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X15" s="16"/>
+      <c r="X15" s="23"/>
       <c r="Y15" s="4" t="s">
         <v>6</v>
       </c>
@@ -5570,34 +5537,34 @@
       <c r="AD15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE15" s="16"/>
+      <c r="AE15" s="23"/>
       <c r="AF15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="AG15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="AH15" s="30" t="s">
+      <c r="AH15" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI15" s="3">
-        <f>COUNTIF(E15:AH15,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ15" s="4">
-        <f>COUNTIF(E15:AH15,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK15" s="4">
-        <f>COUNTIF(E15:AH15,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL15" s="4">
-        <f>COUNTBLANK(E15:AH15)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM15" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -5606,16 +5573,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="4" t="s">
         <v>8</v>
       </c>
@@ -5625,7 +5592,7 @@
       <c r="I16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J16" s="16"/>
+      <c r="J16" s="23"/>
       <c r="K16" s="4" t="s">
         <v>8</v>
       </c>
@@ -5644,7 +5611,7 @@
       <c r="P16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Q16" s="16"/>
+      <c r="Q16" s="23"/>
       <c r="R16" s="4" t="s">
         <v>8</v>
       </c>
@@ -5663,7 +5630,7 @@
       <c r="W16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X16" s="16"/>
+      <c r="X16" s="23"/>
       <c r="Y16" s="4" t="s">
         <v>6</v>
       </c>
@@ -5682,52 +5649,52 @@
       <c r="AD16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="AE16" s="16"/>
+      <c r="AE16" s="23"/>
       <c r="AF16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH16" s="30" t="s">
+      <c r="AH16" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI16" s="3">
-        <f>COUNTIF(E16:AH16,"P")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AJ16" s="4">
-        <f>COUNTIF(E16:AH16,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK16" s="4">
-        <f>COUNTIF(E16:AH16,"L")</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="AL16" s="4">
-        <f>COUNTBLANK(E16:AH16)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM16" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="D17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
+        <v>32</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="4" t="s">
         <v>6</v>
       </c>
@@ -5737,7 +5704,7 @@
       <c r="I17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J17" s="16"/>
+      <c r="J17" s="23"/>
       <c r="K17" s="4" t="s">
         <v>6</v>
       </c>
@@ -5756,7 +5723,7 @@
       <c r="P17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q17" s="16"/>
+      <c r="Q17" s="23"/>
       <c r="R17" s="4" t="s">
         <v>6</v>
       </c>
@@ -5775,7 +5742,7 @@
       <c r="W17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="X17" s="16"/>
+      <c r="X17" s="23"/>
       <c r="Y17" s="4" t="s">
         <v>6</v>
       </c>
@@ -5794,40 +5761,40 @@
       <c r="AD17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AE17" s="16"/>
+      <c r="AE17" s="23"/>
       <c r="AF17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="AG17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AH17" s="30" t="s">
+      <c r="AH17" s="20" t="s">
         <v>6</v>
       </c>
       <c r="AI17" s="3">
-        <f>COUNTIF(E17:AH17,"P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="AJ17" s="4">
-        <f>COUNTIF(E17:AH17,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK17" s="4">
-        <f>COUNTIF(E17:AH17,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AL17" s="4">
-        <f>COUNTBLANK(E17:AH17)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM17" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>15</v>
@@ -5838,154 +5805,139 @@
       <c r="D18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="17"/>
+        <v>39</v>
+      </c>
+      <c r="J18" s="24"/>
       <c r="K18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q18" s="17"/>
+        <v>39</v>
+      </c>
+      <c r="Q18" s="24"/>
       <c r="R18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="X18" s="17"/>
+        <v>39</v>
+      </c>
+      <c r="X18" s="24"/>
       <c r="Y18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AB18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE18" s="17"/>
+        <v>39</v>
+      </c>
+      <c r="AE18" s="24"/>
       <c r="AF18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AG18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH18" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="AH18" s="21" t="s">
+        <v>39</v>
       </c>
       <c r="AI18" s="5">
-        <f>COUNTIF(E18:AH18,"P")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="6">
-        <f>COUNTIF(E18:AH18,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK18" s="6">
-        <f>COUNTIF(E18:AH18,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AL18" s="6">
-        <f>COUNTBLANK(E18:AH18)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AM18" s="11">
-        <f t="shared" ref="AM18" si="2">AI18+AK18+AL18</f>
+        <f t="shared" ref="AM18" si="6">AI18+AK18+AL18</f>
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="AE5:AE18"/>
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="AI3:AM3"/>
     <mergeCell ref="E5:E18"/>
     <mergeCell ref="F5:F18"/>
     <mergeCell ref="J5:J18"/>
     <mergeCell ref="Q5:Q18"/>
     <mergeCell ref="X5:X18"/>
-    <mergeCell ref="AE5:AE18"/>
-    <mergeCell ref="A2:AM2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="AI3:AM3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5 Q5 X5 AE5 G5:I18 K5:P18 R5:W18 Y5:AD18 AF5:AH18">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+  <conditionalFormatting sqref="E5:F5">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>E$3="SUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:AH4 J5 Q5 X5 AE5 G5:I18 K5:P18 R5:W18 Y5:AD18 AF5:AH18">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>E$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+  <conditionalFormatting sqref="J5 Q5 X5 AE5 G5:I18 K5:P18 R5:W18 Y5:AD18 AF5:AH18">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
       <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>E$3="SUN"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>F$3="SUN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6010,112 +5962,112 @@
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:25" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="21"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="29"/>
     </row>
     <row r="3" spans="1:25" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="22" t="str">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="13" t="str">
         <f>TEXT(E4,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="F3" s="18" t="str">
+      <c r="F3" s="12" t="str">
         <f t="shared" ref="F3:T3" si="0">TEXT(F4,"ddd")</f>
         <v>Fri</v>
       </c>
-      <c r="G3" s="18" t="str">
+      <c r="G3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="H3" s="18" t="str">
+      <c r="H3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="I3" s="18" t="str">
+      <c r="I3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="J3" s="18" t="str">
+      <c r="J3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="K3" s="18" t="str">
+      <c r="K3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="L3" s="18" t="str">
+      <c r="L3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="M3" s="18" t="str">
+      <c r="M3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="N3" s="18" t="str">
+      <c r="N3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="P3" s="18" t="str">
+      <c r="P3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="Q3" s="18" t="str">
+      <c r="Q3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="R3" s="18" t="str">
+      <c r="R3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="S3" s="18" t="str">
+      <c r="S3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="T3" s="18" t="str">
+      <c r="T3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="U3" s="32" t="s">
+      <c r="U3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="15"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="35"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6127,58 +6079,58 @@
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="14">
         <v>45778</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="14">
         <v>45779</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="14">
         <v>45780</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="14">
         <v>45781</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="14">
         <v>45782</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="14">
         <v>45783</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="14">
         <v>45784</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="14">
         <v>45785</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="14">
         <v>45786</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="14">
         <v>45787</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="14">
         <v>45788</v>
       </c>
-      <c r="P4" s="23">
+      <c r="P4" s="14">
         <v>45789</v>
       </c>
-      <c r="Q4" s="23">
+      <c r="Q4" s="14">
         <v>45790</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="14">
         <v>45791</v>
       </c>
-      <c r="S4" s="23">
+      <c r="S4" s="14">
         <v>45792</v>
       </c>
-      <c r="T4" s="23">
+      <c r="T4" s="14">
         <v>45793</v>
       </c>
-      <c r="U4" s="33" t="s">
+      <c r="U4" s="22" t="s">
         <v>6</v>
       </c>
       <c r="V4" s="8" t="s">
@@ -6205,10 +6157,10 @@
         <v>14</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>48</v>
+        <v>27</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>47</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>6</v>
@@ -6216,7 +6168,7 @@
       <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -6237,7 +6189,7 @@
       <c r="N5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="P5" s="4" t="s">
@@ -6256,15 +6208,15 @@
         <v>6</v>
       </c>
       <c r="U5" s="3">
-        <f>COUNTIF(E5:T5,"P")</f>
+        <f t="shared" ref="U5:U17" si="1">COUNTIF(E5:T5,"P")</f>
         <v>12</v>
       </c>
       <c r="V5" s="4">
-        <f>COUNTIF(E5:T5,"A")</f>
+        <f t="shared" ref="V5:V17" si="2">COUNTIF(E5:T5,"A")</f>
         <v>0</v>
       </c>
       <c r="W5" s="4">
-        <f>COUNTIF(E5:T5,"L")</f>
+        <f t="shared" ref="W5:W17" si="3">COUNTIF(E5:T5,"L")</f>
         <v>1</v>
       </c>
       <c r="X5" s="4">
@@ -6288,14 +6240,14 @@
       <c r="D6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="34"/>
+      <c r="E6" s="42"/>
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="16"/>
+      <c r="H6" s="23"/>
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
@@ -6314,7 +6266,7 @@
       <c r="N6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="16"/>
+      <c r="O6" s="23"/>
       <c r="P6" s="4" t="s">
         <v>6</v>
       </c>
@@ -6331,23 +6283,23 @@
         <v>6</v>
       </c>
       <c r="U6" s="3">
-        <f>COUNTIF(E6:T6,"P")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="V6" s="4">
-        <f>COUNTIF(E6:T6,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W6" s="4">
-        <f>COUNTIF(E6:T6,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X6" s="4">
-        <f>COUNTBLANK(E6:T6)</f>
+        <f t="shared" ref="X6:X17" si="4">COUNTBLANK(E6:T6)</f>
         <v>3</v>
       </c>
       <c r="Y6" s="10">
-        <f t="shared" ref="Y6:Y17" si="1">U6+W6+X6</f>
+        <f t="shared" ref="Y6:Y17" si="5">U6+W6+X6</f>
         <v>16</v>
       </c>
     </row>
@@ -6356,22 +6308,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="34"/>
+      <c r="E7" s="42"/>
       <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="16"/>
+      <c r="H7" s="23"/>
       <c r="I7" s="4" t="s">
         <v>6</v>
       </c>
@@ -6390,7 +6342,7 @@
       <c r="N7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="16"/>
+      <c r="O7" s="23"/>
       <c r="P7" s="4" t="s">
         <v>6</v>
       </c>
@@ -6407,23 +6359,23 @@
         <v>6</v>
       </c>
       <c r="U7" s="3">
-        <f>COUNTIF(E7:T7,"P")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="V7" s="4">
-        <f>COUNTIF(E7:T7,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W7" s="4">
-        <f>COUNTIF(E7:T7,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X7" s="4">
-        <f>COUNTBLANK(E7:T7)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y7" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6440,14 +6392,14 @@
       <c r="D8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="34"/>
+      <c r="E8" s="42"/>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="16"/>
+      <c r="H8" s="23"/>
       <c r="I8" s="4" t="s">
         <v>8</v>
       </c>
@@ -6466,7 +6418,7 @@
       <c r="N8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O8" s="16"/>
+      <c r="O8" s="23"/>
       <c r="P8" s="4" t="s">
         <v>8</v>
       </c>
@@ -6483,23 +6435,23 @@
         <v>6</v>
       </c>
       <c r="U8" s="3">
-        <f>COUNTIF(E8:T8,"P")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="V8" s="4">
-        <f>COUNTIF(E8:T8,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W8" s="4">
-        <f>COUNTIF(E8:T8,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X8" s="4">
-        <f>COUNTBLANK(E8:T8)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y8" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6511,19 +6463,19 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="34"/>
+      <c r="E9" s="42"/>
       <c r="F9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="23"/>
       <c r="I9" s="4" t="s">
         <v>6</v>
       </c>
@@ -6542,7 +6494,7 @@
       <c r="N9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="16"/>
+      <c r="O9" s="23"/>
       <c r="P9" s="4" t="s">
         <v>6</v>
       </c>
@@ -6559,23 +6511,23 @@
         <v>6</v>
       </c>
       <c r="U9" s="3">
-        <f>COUNTIF(E9:T9,"P")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="V9" s="4">
-        <f>COUNTIF(E9:T9,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W9" s="4">
-        <f>COUNTIF(E9:T9,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X9" s="4">
-        <f>COUNTBLANK(E9:T9)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y9" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6584,22 +6536,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="34"/>
+      <c r="E10" s="42"/>
       <c r="F10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="16"/>
+      <c r="H10" s="23"/>
       <c r="I10" s="4" t="s">
         <v>6</v>
       </c>
@@ -6618,7 +6570,7 @@
       <c r="N10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O10" s="16"/>
+      <c r="O10" s="23"/>
       <c r="P10" s="4" t="s">
         <v>8</v>
       </c>
@@ -6635,23 +6587,23 @@
         <v>6</v>
       </c>
       <c r="U10" s="3">
-        <f>COUNTIF(E10:T10,"P")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="V10" s="4">
-        <f>COUNTIF(E10:T10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W10" s="4">
-        <f>COUNTIF(E10:T10,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X10" s="4">
-        <f>COUNTBLANK(E10:T10)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y10" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6660,22 +6612,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="34"/>
+      <c r="E11" s="42"/>
       <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="16"/>
+      <c r="H11" s="23"/>
       <c r="I11" s="4" t="s">
         <v>6</v>
       </c>
@@ -6694,7 +6646,7 @@
       <c r="N11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O11" s="16"/>
+      <c r="O11" s="23"/>
       <c r="P11" s="4" t="s">
         <v>6</v>
       </c>
@@ -6711,23 +6663,23 @@
         <v>6</v>
       </c>
       <c r="U11" s="3">
-        <f>COUNTIF(E11:T11,"P")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="V11" s="4">
-        <f>COUNTIF(E11:T11,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W11" s="4">
-        <f>COUNTIF(E11:T11,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X11" s="4">
-        <f>COUNTBLANK(E11:T11)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y11" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6744,14 +6696,14 @@
       <c r="D12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="34"/>
+      <c r="E12" s="42"/>
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="16"/>
+      <c r="H12" s="23"/>
       <c r="I12" s="4" t="s">
         <v>6</v>
       </c>
@@ -6770,7 +6722,7 @@
       <c r="N12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O12" s="16"/>
+      <c r="O12" s="23"/>
       <c r="P12" s="4" t="s">
         <v>6</v>
       </c>
@@ -6787,23 +6739,23 @@
         <v>6</v>
       </c>
       <c r="U12" s="3">
-        <f>COUNTIF(E12:T12,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="V12" s="4">
-        <f>COUNTIF(E12:T12,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W12" s="4">
-        <f>COUNTIF(E12:T12,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X12" s="4">
-        <f>COUNTBLANK(E12:T12)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y12" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6820,14 +6772,14 @@
       <c r="D13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="34"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="16"/>
+      <c r="H13" s="23"/>
       <c r="I13" s="4" t="s">
         <v>6</v>
       </c>
@@ -6846,7 +6798,7 @@
       <c r="N13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O13" s="16"/>
+      <c r="O13" s="23"/>
       <c r="P13" s="4" t="s">
         <v>6</v>
       </c>
@@ -6863,23 +6815,23 @@
         <v>6</v>
       </c>
       <c r="U13" s="3">
-        <f>COUNTIF(E13:T13,"P")</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="V13" s="4">
-        <f>COUNTIF(E13:T13,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W13" s="4">
-        <f>COUNTIF(E13:T13,"L")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X13" s="4">
-        <f>COUNTBLANK(E13:T13)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y13" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6896,14 +6848,14 @@
       <c r="D14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="34"/>
+      <c r="E14" s="42"/>
       <c r="F14" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="16"/>
+      <c r="H14" s="23"/>
       <c r="I14" s="4" t="s">
         <v>6</v>
       </c>
@@ -6922,7 +6874,7 @@
       <c r="N14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O14" s="16"/>
+      <c r="O14" s="23"/>
       <c r="P14" s="4" t="s">
         <v>6</v>
       </c>
@@ -6939,23 +6891,23 @@
         <v>6</v>
       </c>
       <c r="U14" s="3">
-        <f>COUNTIF(E14:T14,"P")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="V14" s="4">
-        <f>COUNTIF(E14:T14,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W14" s="4">
-        <f>COUNTIF(E14:T14,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X14" s="4">
-        <f>COUNTBLANK(E14:T14)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y14" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -6964,22 +6916,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="34"/>
+      <c r="E15" s="42"/>
       <c r="F15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="16"/>
+      <c r="H15" s="23"/>
       <c r="I15" s="4" t="s">
         <v>6</v>
       </c>
@@ -6998,7 +6950,7 @@
       <c r="N15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O15" s="16"/>
+      <c r="O15" s="23"/>
       <c r="P15" s="4" t="s">
         <v>6</v>
       </c>
@@ -7015,23 +6967,23 @@
         <v>6</v>
       </c>
       <c r="U15" s="3">
-        <f>COUNTIF(E15:T15,"P")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="V15" s="4">
-        <f>COUNTIF(E15:T15,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W15" s="4">
-        <f>COUNTIF(E15:T15,"L")</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X15" s="4">
-        <f>COUNTBLANK(E15:T15)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y15" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -7040,22 +6992,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="34"/>
+      <c r="E16" s="42"/>
       <c r="F16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="16"/>
+      <c r="H16" s="23"/>
       <c r="I16" s="4" t="s">
         <v>6</v>
       </c>
@@ -7074,7 +7026,7 @@
       <c r="N16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O16" s="16"/>
+      <c r="O16" s="23"/>
       <c r="P16" s="4" t="s">
         <v>6</v>
       </c>
@@ -7091,99 +7043,99 @@
         <v>6</v>
       </c>
       <c r="U16" s="3">
-        <f>COUNTIF(E16:T16,"P")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="V16" s="4">
-        <f>COUNTIF(E16:T16,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W16" s="4">
-        <f>COUNTIF(E16:T16,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X16" s="4">
-        <f>COUNTBLANK(E16:T16)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y16" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="43"/>
+      <c r="F17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="24"/>
+      <c r="I17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O17" s="24"/>
+      <c r="P17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="T17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="U17" s="5">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="O17" s="17"/>
-      <c r="P17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="S17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="T17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="U17" s="5">
-        <f>COUNTIF(E17:T17,"P")</f>
-        <v>12</v>
-      </c>
       <c r="V17" s="6">
-        <f>COUNTIF(E17:T17,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W17" s="6">
-        <f>COUNTIF(E17:T17,"L")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X17" s="6">
-        <f>COUNTBLANK(E17:T17)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Y17" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
@@ -7196,7 +7148,7 @@
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="U3:Y3"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5 O5 F5:G17 I5:N17 P5:T17 E5">
+  <conditionalFormatting sqref="E5 H5 O5 F5:G17 I5:N17 P5:T17">
     <cfRule type="cellIs" dxfId="2" priority="14" operator="equal">
       <formula>"A"</formula>
     </cfRule>
@@ -7204,7 +7156,7 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:T4 H5 O5 F5:G17 I5:N17 P5:T17 E5">
+  <conditionalFormatting sqref="E3:T4 E5 H5 O5 F5:G17 I5:N17 P5:T17">
     <cfRule type="expression" dxfId="0" priority="13">
       <formula>E$3="SUN"</formula>
     </cfRule>
